--- a/output/full_scan/batch_seq0_2026-10-01.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-01.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1049.96689487648</v>
+        <v>1219.96689487648</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>144.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>71.36299928698803</v>
+        <v>71.36299925477466</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26.85684296756294</v>
+        <v>26.85684297960655</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.799793118512346</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.173961421213757</v>
+        <v>1.173961421191493</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8289</v>
+        <v>8046</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>960.2954652391796</v>
+        <v>1175.888617569931</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>51</v>
+        <v>1420</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>70.47401660736593</v>
+        <v>70.12494492366534</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.89626997807333</v>
+        <v>17.71877930133824</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.112487505708142</v>
+        <v>1.697830412014101</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.817912261390657</v>
+        <v>34.63240910544732</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8182</v>
+        <v>8289</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>870.13426360631</v>
+        <v>1160.29546523918</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>44.25</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>69.22288249450725</v>
+        <v>70.47401658540937</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.99838730244414</v>
+        <v>21.89627008534406</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.734845970122263</v>
+        <v>5.112487505708142</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>4</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.5883043758838737</v>
+        <v>0.8179122613795246</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8150</v>
+        <v>8182</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>791.0174207786496</v>
+        <v>1070.13426360631</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>115.5</v>
+        <v>44.25</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>69.27412340791408</v>
+        <v>69.22288249450725</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28.27573121784641</v>
+        <v>15.998387341919</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.701742077864953</v>
+        <v>4.734845970122263</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.668950936885292</v>
+        <v>0.5883043758393719</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8046</v>
+        <v>8150</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>770.8886175699313</v>
+        <v>981.0174207786496</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1420</v>
+        <v>115.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,29 +764,29 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.12494490799226</v>
+        <v>69.2741234014614</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>17.71877919916781</v>
+        <v>28.27573114274154</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.697830412014101</v>
+        <v>1.701742077864953</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>34.63240910633732</v>
+        <v>2.668950936907541</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>734.0477283253914</v>
+        <v>934.0477283253912</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>60.2</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>76.19095930053257</v>
+        <v>76.19095937527067</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37.58599876788621</v>
+        <v>37.58599885465012</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>4.504772832539145</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.6527416711423655</v>
+        <v>0.6527416710199656</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8162</v>
+        <v>8201</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>721.3455453487675</v>
+        <v>929</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>68</v>
+        <v>17.65</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.19324273128463</v>
+        <v>88.95220748384439</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>19.17886301425163</v>
+        <v>50.4016714552104</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.734554534876751</v>
+        <v>8.811343858773768</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.8087498160769809</v>
+        <v>0.5855272989134674</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8054</v>
+        <v>8162</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>686.9501908113562</v>
+        <v>921.3455453487676</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>89.8</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.81843636485849</v>
+        <v>67.19324270573044</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>18.88207890256133</v>
+        <v>19.17886304620908</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.295019081135611</v>
+        <v>1.734554534876751</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.9189209514450823</v>
+        <v>0.8087498163662916</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8043</v>
+        <v>8215</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>684.7906420525545</v>
+        <v>890.1547147518569</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>138.5</v>
+        <v>29.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>52.55226347795497</v>
+        <v>62.74118193235056</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9.966391583578783</v>
+        <v>36.58486081517586</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.016702594769987</v>
+        <v>0.9542227917086812</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,11 +994,11 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4603103945337947</v>
+        <v>0.2938525501302484</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>675.4709043859428</v>
+        <v>875.470904385943</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>34.65</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>74.53790630251959</v>
+        <v>74.53790629271458</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.15891355159995</v>
+        <v>26.15891361103091</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3.766954763560406</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.9255960986333602</v>
+        <v>0.925596098566595</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8215</v>
+        <v>8996</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>675.1547147518569</v>
+        <v>832.6951021329576</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>29.1</v>
+        <v>1565</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.74118197596747</v>
+        <v>61.9210028704772</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.584860815231</v>
+        <v>37.45388089926571</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9542227917086812</v>
+        <v>1.228247219321142</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2938525500968685</v>
+        <v>20.8798559916896</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8042</v>
+        <v>8054</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>652.7421294104239</v>
+        <v>826.9501908113562</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>118</v>
+        <v>89.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.33312858280041</v>
+        <v>63.81843633916156</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>18.13890933997882</v>
+        <v>18.88207892783234</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.173103406276397</v>
+        <v>2.295019081135611</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.6484459418117737</v>
+        <v>0.9189209507774621</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8996</v>
+        <v>8043</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>642.6951021329576</v>
+        <v>824.7906420525545</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1565</v>
+        <v>138.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.92100284916143</v>
+        <v>52.55226347458852</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.45388086056806</v>
+        <v>9.966391652165276</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.228247219321142</v>
+        <v>3.016702594769987</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>20.8798559916896</v>
+        <v>0.4603103945337947</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8147</v>
+        <v>8040</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>638.7799081675496</v>
+        <v>800.1172096982926</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>143.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.2786058141823</v>
+        <v>66.88601721874981</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.8866005158229</v>
+        <v>28.39073775579468</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.073644005350565</v>
+        <v>0.8117209698292676</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.699980874543315</v>
+        <v>1.963776778347448</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8227</v>
+        <v>8042</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>632.9141735297716</v>
+        <v>792.7421294104239</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>363.5</v>
+        <v>118</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>84.25387719272582</v>
+        <v>55.33312858626128</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>52.81301662190545</v>
+        <v>18.13890935256649</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3.23360506958176</v>
+        <v>2.173103406276397</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>11.14829468202795</v>
+        <v>0.6484459418006331</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8111</v>
+        <v>8147</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>629.2047406457277</v>
+        <v>778.7799081675505</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>78</v>
+        <v>143.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.17856684109477</v>
+        <v>57.27860575860376</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.3867151613826</v>
+        <v>28.88660048233661</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3837431959205907</v>
+        <v>3.073644005350565</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0673621870979661</v>
+        <v>1.699980875656013</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8201</v>
+        <v>8070</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>619</v>
+        <v>758.5278528172271</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>17.65</v>
+        <v>50.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>88.95220746271873</v>
+        <v>52.30321444825554</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>50.40167150300576</v>
+        <v>13.5674870185266</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8.811343858773768</v>
+        <v>0.6041901728215459</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.5855272989357214</v>
+        <v>0.0111711984920514</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8299</v>
+        <v>8045</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>617.925399375839</v>
+        <v>738.8708952436328</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2110</v>
+        <v>54.7</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.26386101544029</v>
+        <v>58.47993337207364</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14.54439968353285</v>
+        <v>20.7636474031368</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5569365434939147</v>
+        <v>0.7458597143567028</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>7.494132409011328</v>
+        <v>0.4978328165576609</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8040</v>
+        <v>8050</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>600.1172096982928</v>
+        <v>735.039115726299</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>95.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>66.88601720752051</v>
+        <v>64.01007317804221</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.39073765373436</v>
+        <v>22.84225566268033</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8117209698292676</v>
+        <v>1.167726491657394</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.963776778503241</v>
+        <v>0.8327284432014291</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8103</v>
+        <v>8064</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>599.7128320435717</v>
+        <v>728.2595429870363</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>124</v>
+        <v>143.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>59.08351118705328</v>
+        <v>65.60198432070128</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>37.83962881308881</v>
+        <v>22.95668552856058</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7453292958438206</v>
+        <v>0.6259542987036313</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.161699789536044</v>
+        <v>1.888634489394865</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8089</v>
+        <v>8103</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>586.1789029825434</v>
+        <v>704.7128320435717</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>19.6</v>
+        <v>124</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.14993264419201</v>
+        <v>59.0835112084548</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.46408320259224</v>
+        <v>37.83962876273281</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3995043753308345</v>
+        <v>0.7453292958438206</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1715146735695208</v>
+        <v>-1.161699787896027</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8049</v>
+        <v>8089</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>580.8024026547977</v>
+        <v>701.178902982543</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>24.8</v>
+        <v>19.6</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.71357143058525</v>
+        <v>62.1499326112333</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>16.67002604504003</v>
+        <v>25.46408318804622</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.569564067199991</v>
+        <v>0.3995043753308345</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0790238627651153</v>
+        <v>0.1715146734471214</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8070</v>
+        <v>8049</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>573.5278528172271</v>
+        <v>695.8024026547977</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>50.2</v>
+        <v>24.8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>52.30321434337543</v>
+        <v>54.71357130429372</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>13.56748697833399</v>
+        <v>16.67002580877378</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6041901728215459</v>
+        <v>1.569564067199991</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0111711986589563</v>
+        <v>0.07902386270948231</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8050</v>
+        <v>8438</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>565.039115726299</v>
+        <v>686.5417035820175</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>63.4</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>64.01007312790003</v>
+        <v>72.86595045908452</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22.84225554370768</v>
+        <v>25.62631548665433</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.167726491657394</v>
+        <v>1.369672896787154</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.8327284438245457</v>
+        <v>1.457583779623679</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8064</v>
+        <v>8234</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>558.2595429870363</v>
+        <v>658.8035284856101</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>143.5</v>
+        <v>63</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>65.60198431343623</v>
+        <v>45.92497646137447</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.95668547780446</v>
+        <v>20.09825622682675</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6259542987036313</v>
+        <v>0.7223230989856513</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.888634489528397</v>
+        <v>0.0398483014226709</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8234</v>
+        <v>8227</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>543.8035284856101</v>
+        <v>632.9141735297716</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>63</v>
+        <v>363.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45.92497642739061</v>
+        <v>84.25387719272582</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.09825613662799</v>
+        <v>52.81301662190545</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7223230989856513</v>
+        <v>3.23360506958176</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0398483014226709</v>
+        <v>11.14829468202795</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8438</v>
+        <v>8111</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>516.541703582018</v>
+        <v>629.2047406457277</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>72.86595043150629</v>
+        <v>59.17856684794143</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.62631535142924</v>
+        <v>32.38671520356582</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.369672896787154</v>
+        <v>0.3837431959205907</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.45758377971269</v>
+        <v>0.0673621869867102</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8110</v>
+        <v>8081</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>515.7292042687509</v>
+        <v>624.880755633167</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>48.7</v>
+        <v>255</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.89141642378664</v>
+        <v>52.02395979368243</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>22.98657909474334</v>
+        <v>16.16670683029492</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4908204492749205</v>
+        <v>1.43855639858495</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.5666126390945331</v>
+        <v>0.9520764804854892</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8045</v>
+        <v>8476</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>513.8708952436325</v>
+        <v>622.6316612164937</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>54.7</v>
+        <v>20.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.47993322670127</v>
+        <v>58.25450215277832</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.76364739896772</v>
+        <v>11.02898470851516</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7458597143567028</v>
+        <v>1.067472168101902</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4978328171140159</v>
+        <v>0.113812699695993</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8081</v>
+        <v>8358</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>509.8807556331669</v>
+        <v>620.1821488745034</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>255</v>
+        <v>505</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.0239599613376</v>
+        <v>54.10261314488504</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.16670673495675</v>
+        <v>22.99546724674114</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.43855639858495</v>
+        <v>1.658134876329916</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.9520764790389732</v>
+        <v>-3.077620781422684</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8431</v>
+        <v>8299</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>507.1714609947377</v>
+        <v>617.9253993758387</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>64.7</v>
+        <v>2110</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.52158378214325</v>
+        <v>52.26386099044845</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.1222910817114</v>
+        <v>14.54439969315369</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3632585877852997</v>
+        <v>0.5569365434939147</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1442891683437008</v>
+        <v>7.494132411014625</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8358</v>
+        <v>8072</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>505.1821488745033</v>
+        <v>602.8511729208134</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>505</v>
+        <v>27.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.1026131604592</v>
+        <v>59.83218607954509</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.99546725043974</v>
+        <v>37.98296071938139</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.658134876329916</v>
+        <v>0.3972988554727253</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-3.077620783870625</v>
+        <v>0.1521502145170677</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8171</v>
+        <v>8112</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>494.8617247228884</v>
+        <v>583.780521397231</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>20.7</v>
+        <v>83.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>60.57668258468285</v>
+        <v>42.0861088910598</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.77083714363956</v>
+        <v>22.25796768656701</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5009310655400936</v>
+        <v>0.9553724356770632</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.091472962878521</v>
+        <v>0.0043424226478341</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8072</v>
+        <v>8047</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>487.8511729208136</v>
+        <v>580.9859688946976</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>27.8</v>
+        <v>51</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>59.83218576796118</v>
+        <v>53.25601711664905</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37.98296069095502</v>
+        <v>10.62423628403798</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3972988554727253</v>
+        <v>2.745990896861616</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1521502146283367</v>
+        <v>1.880531462128515</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8068</v>
+        <v>8383</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>484.4144123639149</v>
+        <v>556.3601458524845</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.75</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>58.4584989034587</v>
+        <v>52.307462470796</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.77099113878026</v>
+        <v>12.74331762181485</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7017956203209842</v>
+        <v>0.4662487646839018</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.217912102691205</v>
+        <v>0.4663997503379191</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8476</v>
+        <v>8086</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>482.6316612164936</v>
+        <v>550.0851276565961</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>20.3</v>
+        <v>115</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>58.25450226884166</v>
+        <v>54.53842661631131</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>11.02898469702167</v>
+        <v>15.84058964172502</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.067472168101902</v>
+        <v>1.524361518523123</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1138126996403589</v>
+        <v>1.023919505644183</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8071</v>
+        <v>8482</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>470.3711163521597</v>
+        <v>548.4721697441574</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>22</v>
+        <v>48.85</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.9274691303691</v>
+        <v>52.73635296130252</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12.41641191230785</v>
+        <v>4.392485084295626</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.013075633762888</v>
+        <v>0.1418852290382309</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0833440959930285</v>
+        <v>0.0245948807683534</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8112</v>
+        <v>8213</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>468.780521397231</v>
+        <v>541.3106815720108</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>83.8</v>
+        <v>34</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>42.08610890104895</v>
+        <v>59.6600475012854</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.25796756812484</v>
+        <v>16.98268112720859</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.9553724356770632</v>
+        <v>1.102251071095946</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0043424228481248</v>
+        <v>0.1330766898452676</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8084</v>
+        <v>8499</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>465.6133365279102</v>
+        <v>538.0254566276848</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>24.2</v>
+        <v>256</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.77368565300088</v>
+        <v>51.37575628583792</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>36.1548809270925</v>
+        <v>9.607030743579491</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.961333652791017</v>
+        <v>0.4763223483799501</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,11 +2584,11 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.84879281475502</v>
+        <v>4.579425363800644</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>450.305410082124</v>
+        <v>525.305410082124</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>15.45</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>50.28774110099357</v>
+        <v>50.2877410324369</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.4388306954371</v>
+        <v>22.43883073346458</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>2.408257021100653</v>
@@ -2641,27 +2641,27 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8383</v>
+        <v>8088</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>441.3601458524845</v>
+        <v>523.4019282152376</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>43.65</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.30746248893002</v>
+        <v>49.65490592729508</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>12.74331762036999</v>
+        <v>12.71018707996987</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4662487646839018</v>
+        <v>1.935031344864355</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.466399750237782</v>
+        <v>0.3809271035484647</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8473</v>
+        <v>8110</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>438.789236118895</v>
+        <v>515.7292042687509</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39.05</v>
+        <v>48.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>38.18331186969978</v>
+        <v>57.8914164130869</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.70614712331042</v>
+        <v>22.98657909102322</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6725284952547518</v>
+        <v>0.4908204492749205</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1373422605617578</v>
+        <v>0.5666126390833993</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8482</v>
+        <v>8431</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>433.4721697441573</v>
+        <v>507.1714609947377</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>48.85</v>
+        <v>64.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.73635298815957</v>
+        <v>58.52158387688762</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>4.392485090572899</v>
+        <v>34.12229107562174</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1418852290382309</v>
+        <v>0.3632585877852997</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0245948808128625</v>
+        <v>-0.144289168288068</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>9912</v>
+        <v>8261</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>427.5813565425605</v>
+        <v>502.6370993475942</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>12.95</v>
+        <v>181.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>50.36073091856603</v>
+        <v>52.36767076835285</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>31.65986444677491</v>
+        <v>10.22284767081697</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.2726207516319754</v>
+        <v>1.492999376112703</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.008403776669517001</v>
+        <v>2.109857169740343</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8213</v>
+        <v>8048</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>426.3106815720107</v>
+        <v>501.8742244280081</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>34</v>
+        <v>50.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.66004743636633</v>
+        <v>51.58080121121515</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.98268104342252</v>
+        <v>12.76805876354791</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.102251071095946</v>
+        <v>0.630566428638565</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1330766899009027</v>
+        <v>0.3282094300487281</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8091</v>
+        <v>8038</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>425.1727169037304</v>
+        <v>500.1080847748553</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>215.5</v>
+        <v>33.85</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.5554692234608</v>
+        <v>59.50505133893994</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>12.34654355686</v>
+        <v>25.03591000950208</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5326736528512359</v>
+        <v>0.6816500585252051</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.44611446814231</v>
+        <v>0.3763677598233192</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8086</v>
+        <v>8171</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>410.0851276565971</v>
+        <v>494.8617247228881</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>115</v>
+        <v>20.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.53842656797524</v>
+        <v>60.57668249330772</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15.84058962490305</v>
+        <v>21.77083714884052</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.524361518523123</v>
+        <v>0.5009310655400936</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.023919505421636</v>
+        <v>0.09147296294528071</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8472</v>
+        <v>8096</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>408</v>
+        <v>491.0908962941155</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.2</v>
+        <v>87.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>38.73512425790232</v>
+        <v>34.84312590344156</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28.62878991674214</v>
+        <v>34.98239297374337</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6.441752651227504</v>
+        <v>0.8187242165052779</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.034752807638526</v>
+        <v>0.8401099004246833</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8097</v>
+        <v>8068</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>396.676512157828</v>
+        <v>484.4144123639149</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>48.55</v>
+        <v>17.75</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.86370008879475</v>
+        <v>58.45849893760726</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.67861059286959</v>
+        <v>26.77099118306128</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6896979877806397</v>
+        <v>0.7017956203209842</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,48 +3114,48 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.102902832662989</v>
+        <v>0.2179121026355679</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8183</v>
+        <v>8131</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>395.8634049635195</v>
+        <v>480.6129322449619</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>28.2</v>
+        <v>62.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>44.90268848571781</v>
+        <v>52.74844998587146</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.14537587969442</v>
+        <v>8.558424266831256</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>0.6158154407397529</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0686206104549594</v>
+        <v>0.3905175410262211</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8261</v>
+        <v>8104</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>387.6370993475942</v>
+        <v>473.0592793999995</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>181.5</v>
+        <v>31.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.36767076835285</v>
+        <v>56.46290093715484</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.22284765458772</v>
+        <v>18.64900937751505</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.492999376112703</v>
+        <v>0.7166373844437636</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.109857169740343</v>
+        <v>0.2897443001843864</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8423</v>
+        <v>8071</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>385.7134131001353</v>
+        <v>470.3711163521597</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.90410528712786</v>
+        <v>43.9274690998782</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.4398264932642</v>
+        <v>12.41641186433508</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3860673349369538</v>
+        <v>1.013075633762888</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0052966595767118</v>
+        <v>0.0833440960597899</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8088</v>
+        <v>8084</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>383.4019282152376</v>
+        <v>465.6133365279102</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>43.65</v>
+        <v>24.2</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>49.65490592338574</v>
+        <v>10.77368565300088</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12.71018707102604</v>
+        <v>36.1548809270925</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.935031344864355</v>
+        <v>2.961333652791017</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3809271034817054</v>
+        <v>-1.84879281475502</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8047</v>
+        <v>8473</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>380.9859688946867</v>
+        <v>438.7892361188952</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>51</v>
+        <v>39.05</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.256017119864</v>
+        <v>38.18331179162794</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10.62423624158459</v>
+        <v>27.70614712450903</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>2.745990896861616</v>
+        <v>0.6725284952547518</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.880531462061748</v>
+        <v>0.1373422606285239</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8210</v>
+        <v>9912</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>380.3182126787244</v>
+        <v>427.5813565425605</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>845</v>
+        <v>12.95</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>33.3317485020967</v>
+        <v>50.3607309610657</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.86860807063302</v>
+        <v>31.659864439503</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.482927380320345</v>
+        <v>0.2726207516319754</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.2197391261821195</v>
+        <v>-0.0084037766806441</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8277</v>
+        <v>8091</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>372.768685016401</v>
+        <v>425.1727169037304</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15.5</v>
+        <v>215.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>81.90646756914894</v>
+        <v>47.55546909621946</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>33.41035188376511</v>
+        <v>12.34654356009991</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9910522235688471</v>
+        <v>0.5326736528512359</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.6862356866298587</v>
+        <v>1.446114468364847</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8462</v>
+        <v>8472</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>371.0523453072311</v>
+        <v>408</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>157</v>
+        <v>69.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>37.7540626110973</v>
+        <v>38.73512437669924</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>27.69914864977443</v>
+        <v>28.62878990164112</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.813517465547106</v>
+        <v>6.441752651227504</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.4811023122050923</v>
+        <v>-1.034752807482759</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8104</v>
+        <v>8097</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>368.0592794000013</v>
+        <v>396.6765121578281</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>31.7</v>
+        <v>48.55</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>56.46290066927486</v>
+        <v>41.86370029099609</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18.6490093076174</v>
+        <v>23.67861057535928</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7166373844437636</v>
+        <v>0.6896979877806397</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2897443002622759</v>
+        <v>0.1029028324849493</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8131</v>
+        <v>8093</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>365.6129322449633</v>
+        <v>395.8804966315882</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>62.5</v>
+        <v>25.25</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.74844991534521</v>
+        <v>52.3820292588121</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8.558424017664205</v>
+        <v>12.78266791804226</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6158154407397529</v>
+        <v>0.7657699153965249</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,51 +3644,51 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.3905175413377895</v>
+        <v>-0.0178673287690651</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8048</v>
+        <v>8183</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>361.8742244280102</v>
+        <v>395.8634049635201</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>50.8</v>
+        <v>28.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.58080118742023</v>
+        <v>44.90268847484674</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.76805877713137</v>
+        <v>19.14537594543738</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.630566428638565</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3282094300153567</v>
+        <v>0.0686206104713073</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8038</v>
+        <v>8114</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>360.1080847748554</v>
+        <v>383.6219832013888</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>33.85</v>
+        <v>178</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>59.50505113950711</v>
+        <v>39.65859364662607</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25.0359100096884</v>
+        <v>25.37085129863581</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6816500585252051</v>
+        <v>0.5802967446817733</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.3763677603129069</v>
+        <v>0.8671999372551316</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8443</v>
+        <v>9105</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>357.9912117136051</v>
+        <v>382.0562453262419</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>11.1</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>35.20382771526137</v>
+        <v>48.82110162070762</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>52.23215899374968</v>
+        <v>16.61734680478558</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1245862424073856</v>
+        <v>0.6521197745533306</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0020980488004924</v>
+        <v>-0.0010722083788306</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8069</v>
+        <v>8210</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>353.8416057017649</v>
+        <v>380.3182126787245</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>144</v>
+        <v>845</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.19199365264942</v>
+        <v>33.33174835974326</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>32.54539561321946</v>
+        <v>21.86860807472349</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7377820043244911</v>
+        <v>1.482927380320345</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.889946745361673</v>
+        <v>0.2197391379769371</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8096</v>
+        <v>8277</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>351.0908962941153</v>
+        <v>372.7686850164012</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>87.5</v>
+        <v>15.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>34.84312591057589</v>
+        <v>81.90646752538282</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>34.9823929201667</v>
+        <v>33.41035188955081</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8187242165052779</v>
+        <v>0.9910522235688471</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.840109900524836</v>
+        <v>0.686235686656556</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8155</v>
+        <v>8462</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>345.7065446635688</v>
+        <v>371.0523453072312</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>313.5</v>
+        <v>157</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.47250403421436</v>
+        <v>37.75406272398055</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15.54045758899873</v>
+        <v>27.69914871093685</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.184113468341544</v>
+        <v>1.813517465547106</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-2.630915539788584</v>
+        <v>-0.4811023123163513</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8466</v>
+        <v>8039</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>341.6652593891211</v>
+        <v>370.2766650668816</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>15.15</v>
+        <v>288.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.99420500221668</v>
+        <v>54.46584092694655</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>33.17444828170257</v>
+        <v>18.39502641274561</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3553832867978663</v>
+        <v>1.373964918048951</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.144965924089869</v>
+        <v>-0.7179111256292283</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8926</v>
+        <v>8466</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>338.1286225193643</v>
+        <v>361.6652593891211</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>58.9</v>
+        <v>15.15</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.42782190667947</v>
+        <v>48.99420516282255</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13.14447465147668</v>
+        <v>33.17444823337545</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4395033830280236</v>
+        <v>0.3553832867978663</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2131880659612026</v>
+        <v>0.144965923956343</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8080</v>
+        <v>8443</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>335.0302897989106</v>
+        <v>357.9912117136051</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>28</v>
+        <v>11.1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.11440520330012</v>
+        <v>35.20382796883456</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>38.26127548691876</v>
+        <v>52.23215910082692</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.352496107511947</v>
+        <v>0.1245862424073856</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1475805736146238</v>
+        <v>-0.0020980488116198</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8477</v>
+        <v>8069</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>334.6739043368789</v>
+        <v>353.8416057017649</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>14.2</v>
+        <v>144</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>36.60793915745801</v>
+        <v>37.19199399543493</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21.44579607414904</v>
+        <v>32.54539576689751</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4337806971306546</v>
+        <v>0.7377820043244911</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1012874875041953</v>
+        <v>0.8899467462518293</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8440</v>
+        <v>8155</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>329.39311769973</v>
+        <v>345.7065446635687</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.2</v>
+        <v>313.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.3736193420052</v>
+        <v>43.4725041072386</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.53868899989008</v>
+        <v>15.54045769155878</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8177036207769104</v>
+        <v>1.184113468341544</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0518710785272208</v>
+        <v>-2.63091553945477</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8059</v>
+        <v>8044</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>313.9426347570026</v>
+        <v>343.2543901200361</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>17.55</v>
+        <v>24.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>61.5697852449508</v>
+        <v>48.94010255114812</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25.46627907033526</v>
+        <v>16.75813143516651</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3108661894310468</v>
+        <v>0.5627151691216061</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3976476508585624</v>
+        <v>0.1695974190790928</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8499</v>
+        <v>8926</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>313.0254566276845</v>
+        <v>338.1286225193643</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>256</v>
+        <v>58.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.37575626564186</v>
+        <v>51.42782196734741</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9.60703068089814</v>
+        <v>13.14447458009976</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4763223483799501</v>
+        <v>0.4395033830280236</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>4.579425364023169</v>
+        <v>0.2131880660390862</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8076</v>
+        <v>8080</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>311.8446308938839</v>
+        <v>335.0302897989106</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>21.6</v>
+        <v>28</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.29055194308364</v>
+        <v>43.11440546557957</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.21233757736091</v>
+        <v>38.26127548991035</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6783654511263971</v>
+        <v>0.352496107511947</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0786508701641029</v>
+        <v>-0.1475805737815274</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8101</v>
+        <v>8477</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>310.72252111481</v>
+        <v>334.6739043368789</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>11.05</v>
+        <v>14.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.00473132867424</v>
+        <v>36.60793914039439</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9.768791586341946</v>
+        <v>21.44579611355786</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.172238546884313</v>
+        <v>0.4337806971306546</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1197866176127931</v>
+        <v>-0.1012874874930683</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8114</v>
+        <v>8440</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>308.6219832013888</v>
+        <v>329.3931176997299</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>178</v>
+        <v>20.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.65859356480541</v>
+        <v>50.37361942796152</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25.37085111787044</v>
+        <v>16.5386890810558</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5802967446817733</v>
+        <v>0.8177036207769104</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.8671999370325976</v>
+        <v>0.0518710784493314</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8411</v>
+        <v>8423</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.8827653794386</v>
+        <v>325.7134131001353</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11.9</v>
+        <v>18</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>25.8148741367125</v>
+        <v>50.90410499246781</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>25.49818617838634</v>
+        <v>21.43982651556607</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.688276537943864</v>
+        <v>0.3860673349369538</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0953583585766317</v>
+        <v>0.0052966596323478</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8488</v>
+        <v>8059</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>303.9789273222806</v>
+        <v>313.9426347570026</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>9.84</v>
+        <v>17.55</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.50567551282986</v>
+        <v>61.56978500365775</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>36.47037274631816</v>
+        <v>25.46627902349026</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1159954881516423</v>
+        <v>0.3108661894310468</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0235349792392569</v>
+        <v>0.3976476505725138</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8085</v>
+        <v>8076</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>301.9060883198565</v>
+        <v>311.8446308938839</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>14.6</v>
+        <v>21.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>57.62367390570927</v>
+        <v>42.29055190971828</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.7462513203638</v>
+        <v>23.21233758336195</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5620236827415287</v>
+        <v>0.6783654511263971</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1150257356744669</v>
+        <v>0.07865087009733911</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8163</v>
+        <v>8101</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>300.3775175617945</v>
+        <v>310.72252111481</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>30.6</v>
+        <v>11.05</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.3062917584353</v>
+        <v>46.00473132404378</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.84990252808971</v>
+        <v>9.768791691926122</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.287947038967229</v>
+        <v>1.172238546884313</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1516366800786693</v>
+        <v>-0.1197866176127931</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8074</v>
+        <v>8404</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>298.6544076536788</v>
+        <v>307.9866750063926</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>51.8</v>
+        <v>13.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.5038781819163</v>
+        <v>25.43363093485908</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.08091268257607</v>
+        <v>47.21321271884154</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6647960753040113</v>
+        <v>0.7519798672014748</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>2</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2884067169548081</v>
+        <v>-0.0353908407606922</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8464</v>
+        <v>8411</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>291.1260512501327</v>
+        <v>307.8827653794386</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>362.5</v>
+        <v>11.9</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>42.04079383466812</v>
+        <v>25.81487424973099</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.36086171742773</v>
+        <v>25.4981862051077</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5159211735058915</v>
+        <v>0.688276537943864</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.9736834191938728</v>
+        <v>-0.09535835859888479</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8932</v>
+        <v>9930</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>286.098059423436</v>
+        <v>307.5933207013325</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>91.8</v>
+        <v>60.2</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,49 +4845,49 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.31096604144364</v>
+        <v>27.03214570547557</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.24064907474033</v>
+        <v>27.31429846487958</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4146459216225267</v>
+        <v>0.5360164327660453</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.6342388247780915</v>
+        <v>-0.0947802734256034</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8092</v>
+        <v>8488</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>270.1006812424801</v>
+        <v>303.9789273222806</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.55</v>
+        <v>9.84</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>40.53728975568949</v>
+        <v>46.50567166465199</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15.17900951364661</v>
+        <v>36.47037256731433</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6457154603091121</v>
+        <v>0.1159954881516423</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0028638063342023</v>
+        <v>-0.0235349792726383</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9105</v>
+        <v>8085</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>267.0562453262413</v>
+        <v>301.9060883198565</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.82110166081045</v>
+        <v>57.62367388997445</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.61734677109505</v>
+        <v>16.74625126020253</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6521197745533306</v>
+        <v>0.5620236827415287</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0010722083677035</v>
+        <v>-0.1150257357301031</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8429</v>
+        <v>8163</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>261.3527271803606</v>
+        <v>300.3775175617945</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>5.91</v>
+        <v>30.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.1365858876586</v>
+        <v>50.30629176664368</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>7.743176790319951</v>
+        <v>13.84990261307125</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7003123612934491</v>
+        <v>1.287947038967229</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0023552536423712</v>
+        <v>0.1516366800119053</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8271</v>
+        <v>8478</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>261.292990868752</v>
+        <v>299.6597660612881</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>201</v>
+        <v>141.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.57833954534589</v>
+        <v>48.30463847357166</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.75759701548279</v>
+        <v>7.599629357002919</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4800750681613554</v>
+        <v>0.7030916253673001</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.531632160667403</v>
+        <v>0.1994341563976671</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8093</v>
+        <v>8074</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>255.8804966315882</v>
+        <v>298.6544076536784</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>25.25</v>
+        <v>51.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.38202927397099</v>
+        <v>47.50387830935204</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.78266789819318</v>
+        <v>16.08091270410822</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7657699153965249</v>
+        <v>0.6647960753040113</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0178673288072078</v>
+        <v>0.2884067172218594</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8454</v>
+        <v>8464</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>255.3519617909332</v>
+        <v>291.1260512501325</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>239</v>
+        <v>362.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.49370129065801</v>
+        <v>42.04079386856004</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.72359406288222</v>
+        <v>13.3608618139295</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6386912950548053</v>
+        <v>0.5159211735058915</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1883115775420663</v>
+        <v>-0.9736834207517108</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8176</v>
+        <v>8932</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>250.4422903962673</v>
+        <v>286.098059423436</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.4136490265199</v>
+        <v>44.31096585005773</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>25.36511781174063</v>
+        <v>19.24064911247319</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5012135759391227</v>
+        <v>0.4146459216225267</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0058085231979627</v>
+        <v>0.6342388249687891</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8102</v>
+        <v>8454</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>241.2304384423641</v>
+        <v>275.3519617909332</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.63319858450716</v>
+        <v>43.49370139285048</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6.749210152485235</v>
+        <v>10.72359402516536</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2490923696779858</v>
+        <v>0.6386912950548053</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.4934124596648535</v>
+        <v>0.188311576985714</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>9930</v>
+        <v>8092</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>232.5933207013321</v>
+        <v>270.1006812424801</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>60.2</v>
+        <v>12.55</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>27.03214564564152</v>
+        <v>40.53729059949812</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>27.31429848608784</v>
+        <v>15.1790095688029</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5360164327660453</v>
+        <v>0.6457154603091121</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0947802733810954</v>
+        <v>-0.0028638063342023</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8487</v>
+        <v>8429</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>231.2264663116169</v>
+        <v>261.3527271803613</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>70.3</v>
+        <v>5.91</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.80515902554488</v>
+        <v>44.13658575439476</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.14676014870543</v>
+        <v>7.743176790319951</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.788182497369879</v>
+        <v>0.7003123612934491</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0927710140617565</v>
+        <v>0.0023552536490478</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8044</v>
+        <v>8271</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>228.254390120036</v>
+        <v>261.2929908687516</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.2</v>
+        <v>201</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>48.94010264818521</v>
+        <v>39.57833953910287</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.75813143516651</v>
+        <v>13.75759698710993</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5627151691216061</v>
+        <v>0.4800750681613554</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1695974190345869</v>
+        <v>-0.531632160422598</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8422</v>
+        <v>9110</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>220.7780907196766</v>
+        <v>252.014991282016</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>25.6</v>
+        <v>2.98</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.33429508850598</v>
+        <v>52.23503353792645</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.877439730836603</v>
+        <v>5.224108274247527</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7249384455850456</v>
+        <v>0.4787279320383391</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0384713621097496</v>
+        <v>0.1114607467276429</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8039</v>
+        <v>8176</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>215.2766650668816</v>
+        <v>250.4422903962673</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>288.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>54.46584091910123</v>
+        <v>40.41364911786329</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>18.39502640622948</v>
+        <v>25.36511790862721</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.373964918048951</v>
+        <v>0.5012135759391227</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.717911125651459</v>
+        <v>-0.0058085232424719</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8404</v>
+        <v>8102</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>212.9866750063926</v>
+        <v>241.2304384423641</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>13.3</v>
+        <v>59</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>25.43363089684152</v>
+        <v>50.63319858335105</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>47.2132127253674</v>
+        <v>6.749210170204164</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7519798672014748</v>
+        <v>0.2490923696779858</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,11 +5605,11 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0353908407384372</v>
+        <v>-0.4934124592420272</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>211.3242860239825</v>
+        <v>231.3242860239825</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>45.6</v>
@@ -5640,25 +5640,25 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.53237703736796</v>
+        <v>50.53237633496367</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.06118646798102</v>
+        <v>11.06118679916275</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.5831950090960973</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1121850490487516</v>
+        <v>-0.1121850481140735</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8390</v>
+        <v>8487</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>210.8297136638801</v>
+        <v>231.2264663116169</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>90.3</v>
+        <v>70.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>36.65893245703047</v>
+        <v>43.8051590776908</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.82347551539159</v>
+        <v>12.14676022344466</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6819425547221035</v>
+        <v>2.788182497369879</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1162112480037571</v>
+        <v>0.09277101399498849</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8410</v>
+        <v>8422</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>194.8433130879637</v>
+        <v>220.7780907196766</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>27.8</v>
+        <v>25.6</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>28.55503654438539</v>
+        <v>42.33429446150093</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>43.34438507540706</v>
+        <v>8.87743991888151</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.584755185806929</v>
+        <v>0.7249384455850456</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.09655919384297081</v>
+        <v>-0.0384713623004471</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8087</v>
+        <v>8067</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>192.5209121741572</v>
+        <v>213.0286036798882</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>23.6</v>
+        <v>12</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.86466757112237</v>
+        <v>47.93314847875598</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>6.128718708782092</v>
+        <v>15.3253502328429</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9999502724360112</v>
+        <v>0.2930096274591879</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1968187934348361</v>
+        <v>0.0556720767376083</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8940</v>
+        <v>8390</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>184.9231241659276</v>
+        <v>210.8297136638801</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15.05</v>
+        <v>90.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.24177284628686</v>
+        <v>36.65893221396432</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.73950002115732</v>
+        <v>20.823475521793</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3083460890594311</v>
+        <v>0.6819425547221035</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0528132656725609</v>
+        <v>-0.1162112475809358</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8463</v>
+        <v>8249</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>174.5212624083751</v>
+        <v>207.6333497265446</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>21.2</v>
+        <v>39.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>49.14470847901522</v>
+        <v>46.9805036890122</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>23.01953995334474</v>
+        <v>19.76780593687974</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4407917667042846</v>
+        <v>0.5088175964959554</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.008686886581563</v>
+        <v>0.2319685537360578</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>9136</v>
+        <v>8940</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>169.5560119953331</v>
+        <v>204.9231241659276</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>15.05</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>27.86623249752958</v>
+        <v>49.24177293150654</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.90795753402921</v>
+        <v>10.7394999922212</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.535380971662711</v>
+        <v>0.3083460890594311</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0176906508555592</v>
+        <v>0.0528132656503048</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8481</v>
+        <v>8410</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>151.5078796513094</v>
+        <v>194.8433130879639</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>40.65</v>
+        <v>27.8</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.49629064644871</v>
+        <v>28.55503673969299</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>9.206620358032644</v>
+        <v>43.3443847233149</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.8403635973164389</v>
+        <v>0.584755185806929</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0428141411854392</v>
+        <v>-0.09655919443270621</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8341</v>
+        <v>8463</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>146.2141738683997</v>
+        <v>194.5212624083751</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>74.2</v>
+        <v>21.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.27198581973892</v>
+        <v>49.14470841641204</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.79451499215096</v>
+        <v>23.01953997835906</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7747500604069887</v>
+        <v>0.4407917667042846</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.016048893188405</v>
+        <v>-0.008686886559307799</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8374</v>
+        <v>8087</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>133.9089477152934</v>
+        <v>192.5209121741572</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>23.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.39341103561254</v>
+        <v>49.8646675300844</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.03481369924107</v>
+        <v>6.128718750864398</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4907093218030992</v>
+        <v>0.9999502724360112</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0028205618560157</v>
+        <v>0.196818793635126</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9955</v>
+        <v>9136</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>127.8176967208418</v>
+        <v>189.5560119953331</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23.1</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>40.9296594911377</v>
+        <v>27.86623243444875</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.17687004625654</v>
+        <v>19.90795752204946</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.710377521542678</v>
+        <v>0.535380971662711</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.017983784057404</v>
+        <v>-0.0176906508288526</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8455</v>
+        <v>8374</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>125.7405720382076</v>
+        <v>153.9089477152936</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>22.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.40131515868084</v>
+        <v>44.39341069848495</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>8.668340618879521</v>
+        <v>9.034813868602054</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5888472333994151</v>
+        <v>0.4907093218030992</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.3486860657361349</v>
+        <v>-0.0028205605207622</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>9103</v>
+        <v>8481</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>113.572354115436</v>
+        <v>151.5078796513095</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>4.94</v>
+        <v>40.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.49392862423103</v>
+        <v>44.49629063106326</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>9.903567129098192</v>
+        <v>9.206620358032646</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.952816387454403</v>
+        <v>0.8403635973164389</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0018067447812769</v>
+        <v>-0.0428141411520559</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8367</v>
+        <v>8341</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>102.4886444058376</v>
+        <v>146.2141738683997</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>40.8</v>
+        <v>74.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>52.9534884537257</v>
+        <v>39.27198596417904</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.52979436966325</v>
+        <v>15.79451507658098</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8524639105366928</v>
+        <v>0.7747500604069887</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0196201804299112</v>
+        <v>0.0160488929881303</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8291</v>
+        <v>9955</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>98.54495341284276</v>
+        <v>127.817696720841</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>28.35</v>
+        <v>23.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.36554573837795</v>
+        <v>40.92965917862622</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6.245993145114719</v>
+        <v>12.17687004808754</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.14920839102852</v>
+        <v>0.710377521542678</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0882497139497673</v>
+        <v>-0.0179837840017684</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8249</v>
+        <v>8455</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>97.63334972654545</v>
+        <v>125.7405720382067</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>39.4</v>
+        <v>22.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.9805036890122</v>
+        <v>50.40131515966298</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.76780595376464</v>
+        <v>8.668340512311078</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5088175964959554</v>
+        <v>0.5888472333994151</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2319685536470461</v>
+        <v>0.3486860657806424</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>9110</v>
+        <v>9103</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>82.01499128201607</v>
+        <v>113.572354115436</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>2.98</v>
+        <v>4.94</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>52.23503352790254</v>
+        <v>39.49392866354989</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>5.224108276617634</v>
+        <v>9.903567146240716</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4787279320383391</v>
+        <v>0.952816387454403</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1114607467610245</v>
+        <v>0.0018067447746006</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8222</v>
+        <v>8367</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>78.03874794978651</v>
+        <v>102.4886444058379</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>35.55</v>
+        <v>40.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.01543794408362</v>
+        <v>52.95348848377056</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>10.99163243142216</v>
+        <v>16.52979432710109</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.381235223703961</v>
+        <v>0.8524639105366928</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.130440899968018</v>
+        <v>-0.0196201804410434</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8478</v>
+        <v>8291</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>74.65976606128801</v>
+        <v>98.54495341284276</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>141.5</v>
+        <v>28.35</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>48.30463766103352</v>
+        <v>39.36554573837795</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>7.59962923523854</v>
+        <v>6.245993145114719</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.7030916253673001</v>
+        <v>1.14920839102852</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1994341585118089</v>
+        <v>0.0882497139497673</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8067</v>
+        <v>8467</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>73.02860367988821</v>
+        <v>82.86127167242213</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>12</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>47.93314833787844</v>
+        <v>43.21216830765666</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.32535025553199</v>
+        <v>8.129692617738698</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2930096274591879</v>
+        <v>0.4638736384721529</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0556720767709921</v>
+        <v>0.5879622278865853</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>8467</v>
+        <v>8222</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>62.86127167242224</v>
+        <v>78.03874794978651</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>88.09999999999999</v>
+        <v>35.55</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>43.21216812424792</v>
+        <v>44.01543781512176</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8.129692597214518</v>
+        <v>10.9916324677256</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4638736384721529</v>
+        <v>0.381235223703961</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.5879622271077025</v>
+        <v>0.1304409000347856</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
